--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27000" windowHeight="11580" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商编码</t>
     </r>
     <r>
@@ -49,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商名称</t>
     </r>
     <r>
@@ -441,7 +455,7 @@
     <t>国家全部填写简称，如：中华人民共和国，填写中国</t>
   </si>
   <si>
-    <t>省、市、区全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可。</t>
+    <t>省、市、区全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可,地址为北京，上海等直辖市史，需将市名填入”省“栏，”市“栏需填写”市辖区“。</t>
   </si>
   <si>
     <t>付款方式填写新增页面上的下拉项，一般为：银行转账、银行承兑汇票</t>
@@ -1715,29 +1729,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
+    <col min="9" max="9" width="15.225" customWidth="1"/>
     <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
-    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
+    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="21" width="14.6666666666667" customWidth="1"/>
     <col min="22" max="22" width="18.3333333333333" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="22.4444444444444" customWidth="1"/>
+    <col min="24" max="24" width="22.4416666666667" customWidth="1"/>
     <col min="25" max="25" width="20.3333333333333" customWidth="1"/>
     <col min="26" max="26" width="14.6666666666667" customWidth="1"/>
-    <col min="27" max="27" width="19.4444444444444" customWidth="1"/>
+    <col min="27" max="27" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:27">
@@ -1910,9 +1924,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="100.777777777778" style="1" customWidth="1"/>
+    <col min="1" max="1" width="100.775" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
@@ -1945,7 +1959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="31.2" spans="1:1">
+    <row r="7" ht="28.5" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="11580" activeTab="1"/>
+    <workbookView windowWidth="27000" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="11580"/>
+    <workbookView windowWidth="27240" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>对账开始日期和对账结束日期输入格式为：2024-06-11</t>
+  </si>
+  <si>
+    <t>税率直接输入数字即可，如“25.5%”只需输入“25.5”</t>
   </si>
 </sst>
 </file>
@@ -1167,12 +1170,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1755,118 +1761,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:27">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:27">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="6"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1979,7 +1985,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1"/>
+    <row r="11" ht="28" customHeight="1" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="12" ht="28" customHeight="1"/>
     <row r="13" ht="28" customHeight="1"/>
     <row r="14" ht="28" customHeight="1"/>

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27240" windowHeight="12165"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
@@ -130,6 +130,24 @@
     <t>负责人</t>
   </si>
   <si>
+    <t>地区</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
+    <t>省</t>
+  </si>
+  <si>
+    <t>市</t>
+  </si>
+  <si>
+    <t>区</t>
+  </si>
+  <si>
+    <t>地址</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -138,7 +156,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>地区</t>
+      <t>电话</t>
     </r>
     <r>
       <rPr>
@@ -160,7 +178,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>国家</t>
+      <t>手机</t>
     </r>
     <r>
       <rPr>
@@ -174,6 +192,21 @@
     </r>
   </si>
   <si>
+    <t>传真</t>
+  </si>
+  <si>
+    <t>邮政编码</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>网址</t>
+  </si>
+  <si>
+    <t>渠道类型</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -182,7 +215,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>省</t>
+      <t>付款方式</t>
     </r>
     <r>
       <rPr>
@@ -204,7 +237,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>市</t>
+      <t>付款周期</t>
     </r>
     <r>
       <rPr>
@@ -226,7 +259,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>区</t>
+      <t>对账开始日期</t>
     </r>
     <r>
       <rPr>
@@ -248,7 +281,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>地址</t>
+      <t>对账结束日期</t>
     </r>
     <r>
       <rPr>
@@ -270,7 +303,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>电话</t>
+      <t>税率</t>
     </r>
     <r>
       <rPr>
@@ -284,153 +317,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <t>传真</t>
-  </si>
-  <si>
-    <t>邮政编码</t>
-  </si>
-  <si>
-    <t>邮箱</t>
-  </si>
-  <si>
-    <t>网址</t>
-  </si>
-  <si>
-    <t>渠道类型</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>付款方式</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>付款周期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对账开始日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对账结束日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>税率</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -464,7 +350,7 @@
     <t>付款周期一般为：30天、45天、60天、70天、90天，详见新建供应商维护的付款周期下拉项</t>
   </si>
   <si>
-    <t>对账开始日期和对账结束日期输入格式为：2024-06-11</t>
+    <t>对账开始日期和对账结束日期输入格式为：06-11</t>
   </si>
   <si>
     <t>税率直接输入数字即可，如“25.5%”只需输入“25.5”</t>

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,19 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>序号</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>供应商编码</t>
     </r>
     <r>
@@ -56,13 +49,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>供应商名称</t>
     </r>
     <r>
@@ -204,7 +190,48 @@
     <t>网址</t>
   </si>
   <si>
-    <t>渠道类型</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对账开始日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对账结束日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -251,6 +278,9 @@
     </r>
   </si>
   <si>
+    <t>开票类型</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -259,7 +289,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>对账开始日期</t>
+      <t>税率</t>
     </r>
     <r>
       <rPr>
@@ -273,48 +303,25 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对账结束日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>税率</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>认定日期</t>
+  </si>
+  <si>
+    <t>开户银行</t>
+  </si>
+  <si>
+    <t>银行账号</t>
+  </si>
+  <si>
+    <t>渠道类型</t>
+  </si>
+  <si>
+    <t>运输方式</t>
+  </si>
+  <si>
+    <t>运输时间（天）</t>
+  </si>
+  <si>
+    <t>等级</t>
   </si>
   <si>
     <t>备注</t>
@@ -323,37 +330,91 @@
     <t>1</t>
   </si>
   <si>
-    <t>产品编码：需根据编码规则设置中，如果是自动生成，则无需填写，如果是手动输入，则必须输入</t>
-  </si>
-  <si>
-    <t>供应商编码唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
-  </si>
-  <si>
-    <t>电话和手机二选一，必填一项</t>
-  </si>
-  <si>
-    <t>所属分类填写供应商分类名称</t>
-  </si>
-  <si>
-    <t>地区填写国内或国外</t>
-  </si>
-  <si>
-    <t>国家全部填写简称，如：中华人民共和国，填写中国</t>
-  </si>
-  <si>
-    <t>省、市、区全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可,地址为北京，上海等直辖市史，需将市名填入”省“栏，”市“栏需填写”市辖区“。</t>
-  </si>
-  <si>
-    <t>付款方式填写新增页面上的下拉项，一般为：银行转账、银行承兑汇票</t>
-  </si>
-  <si>
-    <t>付款周期一般为：30天、45天、60天、70天、90天，详见新建供应商维护的付款周期下拉项</t>
-  </si>
-  <si>
-    <t>对账开始日期和对账结束日期输入格式为：06-11</t>
-  </si>
-  <si>
-    <t>税率直接输入数字即可，如“25.5%”只需输入“25.5”</t>
+    <t>国内</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>浙江省</t>
+  </si>
+  <si>
+    <t>宁波市</t>
+  </si>
+  <si>
+    <t>鄞州区</t>
+  </si>
+  <si>
+    <t>11-20</t>
+  </si>
+  <si>
+    <t>11-25</t>
+  </si>
+  <si>
+    <t>现金</t>
+  </si>
+  <si>
+    <t>30天</t>
+  </si>
+  <si>
+    <t>增值税专用发票</t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>快递</t>
+  </si>
+  <si>
+    <t>供应商编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
+  </si>
+  <si>
+    <t>电话和手机：二选一，必填一项</t>
+  </si>
+  <si>
+    <t>所属分类：填写供应商分类名称</t>
+  </si>
+  <si>
+    <t>认定日期：输入格式，如：yyyy-MM-dd</t>
+  </si>
+  <si>
+    <t>等级：对应页面上的等级</t>
+  </si>
+  <si>
+    <t>地区：填写国内或国外</t>
+  </si>
+  <si>
+    <t>国家：全部填写简称，如：中华人民共和国，填写中国</t>
+  </si>
+  <si>
+    <t>省、市、区：全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可。</t>
+  </si>
+  <si>
+    <t>渠道类型：对应页面下拉的渠道类型</t>
+  </si>
+  <si>
+    <t>运输方式：对应页面下拉的运输方式</t>
+  </si>
+  <si>
+    <t>运输时间（天 ）：输入整数</t>
+  </si>
+  <si>
+    <t>付款方式：填写新增页面上的下拉项，一般为：银行转账、银行承兑汇票</t>
+  </si>
+  <si>
+    <t>付款周期：一般为：30天、45天、60天、70天、90天，详见新建供应商维护的付款周期下拉项</t>
+  </si>
+  <si>
+    <t>对账开始日期和对账结束日期：输入格式为：06-11</t>
+  </si>
+  <si>
+    <t>开票类型：对应页面下拉的开票类型</t>
+  </si>
+  <si>
+    <t>税率：对应页面下拉税率，如：13%</t>
   </si>
 </sst>
 </file>
@@ -1056,15 +1117,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1076,13 +1137,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1620,33 +1684,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AH48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.4416666666667" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.775" customWidth="1"/>
-    <col min="8" max="8" width="10.225" customWidth="1"/>
-    <col min="9" max="9" width="15.225" customWidth="1"/>
+    <col min="1" max="1" width="7.33333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
     <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
-    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
+    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
+    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.775" customWidth="1"/>
-    <col min="15" max="21" width="14.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="18.3333333333333" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="22.4416666666667" customWidth="1"/>
-    <col min="25" max="25" width="20.3333333333333" customWidth="1"/>
-    <col min="26" max="26" width="14.6666666666667" customWidth="1"/>
-    <col min="27" max="27" width="19.4416666666667" customWidth="1"/>
+    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="15" max="20" width="14.6666666666667" customWidth="1"/>
+    <col min="21" max="21" width="20.6666666666667" customWidth="1"/>
+    <col min="22" max="23" width="21.1111111111111" customWidth="1"/>
+    <col min="24" max="29" width="19.1111111111111" customWidth="1"/>
+    <col min="30" max="30" width="14.6666666666667" customWidth="1"/>
+    <col min="31" max="31" width="16.4444444444444" customWidth="1"/>
+    <col min="32" max="32" width="17.3333333333333" customWidth="1"/>
+    <col min="33" max="33" width="15.8888888888889" customWidth="1"/>
+    <col min="34" max="34" width="26.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:27">
+    <row r="1" ht="25" customHeight="1" spans="1:34">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1725,40 +1791,94 @@
       <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:27">
+    <row r="2" ht="20" customHeight="1" spans="1:34">
       <c r="A2" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="8"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="6"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1815,72 +1935,92 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="100.775" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:1">
+    <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:1">
-      <c r="A11" s="2" t="s">
-        <v>38</v>
+      <c r="A11" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1"/>
-    <row r="13" ht="28" customHeight="1"/>
-    <row r="14" ht="28" customHeight="1"/>
-    <row r="15" ht="28" customHeight="1"/>
-    <row r="16" ht="28" customHeight="1"/>
+    <row r="12" ht="28" customHeight="1" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1"/>
@@ -1890,6 +2030,10 @@
     <row r="23" ht="28" customHeight="1"/>
     <row r="24" ht="28" customHeight="1"/>
     <row r="25" ht="28" customHeight="1"/>
+    <row r="26" ht="28" customHeight="1"/>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="28" customHeight="1"/>
+    <row r="29" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商编码</t>
     </r>
     <r>
@@ -49,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商名称</t>
     </r>
     <r>
@@ -318,7 +332,7 @@
     <t>运输方式</t>
   </si>
   <si>
-    <t>运输时间（天）</t>
+    <t>运输时间(天)</t>
   </si>
   <si>
     <t>等级</t>
@@ -1685,31 +1699,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
+    <col min="9" max="9" width="15.225" customWidth="1"/>
     <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
-    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
+    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="20" width="14.6666666666667" customWidth="1"/>
     <col min="21" max="21" width="20.6666666666667" customWidth="1"/>
-    <col min="22" max="23" width="21.1111111111111" customWidth="1"/>
-    <col min="24" max="29" width="19.1111111111111" customWidth="1"/>
+    <col min="22" max="23" width="21.1083333333333" customWidth="1"/>
+    <col min="24" max="29" width="19.1083333333333" customWidth="1"/>
     <col min="30" max="30" width="14.6666666666667" customWidth="1"/>
-    <col min="31" max="31" width="16.4444444444444" customWidth="1"/>
+    <col min="31" max="31" width="16.4416666666667" customWidth="1"/>
     <col min="32" max="32" width="17.3333333333333" customWidth="1"/>
-    <col min="33" max="33" width="15.8888888888889" customWidth="1"/>
-    <col min="34" max="34" width="26.2222222222222" customWidth="1"/>
+    <col min="33" max="33" width="15.8916666666667" customWidth="1"/>
+    <col min="34" max="34" width="26.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:34">
@@ -1936,9 +1950,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="供应商导入模板" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商编码</t>
     </r>
     <r>
@@ -49,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商名称</t>
     </r>
     <r>
@@ -91,26 +105,7 @@
     <t>英文名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>联系人</t>
   </si>
   <si>
     <t>负责人</t>
@@ -134,48 +129,10 @@
     <t>地址</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>手机</t>
   </si>
   <si>
     <t>传真</t>
@@ -372,7 +329,7 @@
     <t>供应商编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
   </si>
   <si>
-    <t>电话和手机：二选一，必填一项</t>
+    <t>电话和手机：非必填</t>
   </si>
   <si>
     <t>所属分类：填写供应商分类名称</t>
@@ -1685,31 +1642,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
+    <col min="9" max="9" width="15.225" customWidth="1"/>
     <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
-    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
+    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="20" width="14.6666666666667" customWidth="1"/>
     <col min="21" max="21" width="20.6666666666667" customWidth="1"/>
-    <col min="22" max="23" width="21.1111111111111" customWidth="1"/>
-    <col min="24" max="29" width="19.1111111111111" customWidth="1"/>
+    <col min="22" max="23" width="21.1083333333333" customWidth="1"/>
+    <col min="24" max="29" width="19.1083333333333" customWidth="1"/>
     <col min="30" max="30" width="14.6666666666667" customWidth="1"/>
-    <col min="31" max="31" width="16.4444444444444" customWidth="1"/>
+    <col min="31" max="31" width="16.4416666666667" customWidth="1"/>
     <col min="32" max="32" width="17.3333333333333" customWidth="1"/>
-    <col min="33" max="33" width="15.8888888888889" customWidth="1"/>
-    <col min="34" max="34" width="26.2222222222222" customWidth="1"/>
+    <col min="33" max="33" width="15.8916666666667" customWidth="1"/>
+    <col min="34" max="34" width="26.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:34">
@@ -1936,9 +1893,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">

--- a/public/static/供应商导入模板.xlsx
+++ b/public/static/供应商导入模板.xlsx
@@ -105,26 +105,7 @@
     <t>英文名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>联系人</t>
   </si>
   <si>
     <t>负责人</t>
@@ -148,48 +129,10 @@
     <t>地址</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>手机</t>
   </si>
   <si>
     <t>传真</t>
